--- a/data/trans_orig/IP16A05-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16A05-Clase-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>594</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>5137</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5883</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12063</t>
+          <t>12514</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16148</t>
+          <t>16325</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20860</t>
+          <t>20868</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30750</t>
+          <t>30612</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36009</t>
+          <t>35988</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>605</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2977</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10163</t>
+          <t>10561</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14676</t>
+          <t>14244</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18824</t>
+          <t>18825</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10564</t>
+          <t>10837</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16385</t>
+          <t>16392</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27124</t>
+          <t>26726</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34310</t>
+          <t>34516</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,57%</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>5950</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>679</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6248</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15861</t>
+          <t>16002</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21285</t>
+          <t>21258</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26814</t>
+          <t>27014</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32356</t>
+          <t>32383</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9823</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9786</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6594</t>
+          <t>6687</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16884</t>
+          <t>17101</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27862</t>
+          <t>27994</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35063</t>
+          <t>34957</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29003</t>
+          <t>28887</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36054</t>
+          <t>36097</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59591</t>
+          <t>59374</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>69881</t>
+          <t>69788</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,26%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>504</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>2491</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>601</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5473</t>
+          <t>6043</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13658</t>
+          <t>14361</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18332</t>
+          <t>18349</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20842</t>
+          <t>21408</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37279</t>
+          <t>36709</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42153</t>
+          <t>42151</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15495</t>
+          <t>15320</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9162</t>
+          <t>9719</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21161</t>
+          <t>21115</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17355</t>
+          <t>17882</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32469</t>
+          <t>32954</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>94239</t>
+          <t>94414</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>103766</t>
+          <t>104038</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>114136</t>
+          <t>114182</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>126135</t>
+          <t>125578</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>212561</t>
+          <t>212076</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>227675</t>
+          <t>227148</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,7%</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8062</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9892</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16286</t>
+          <t>16272</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13916</t>
+          <t>14374</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20554</t>
+          <t>20522</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33006</t>
+          <t>33107</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40738</t>
+          <t>40368</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10732</t>
+          <t>10350</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12058</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,75%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12171</t>
+          <t>12553</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19301</t>
+          <t>19346</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8090</t>
+          <t>8822</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22934</t>
+          <t>22832</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30917</t>
+          <t>31069</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,79%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>822</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>6179</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>697</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5643</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2392</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>8521</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>35,58%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5643</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10730</t>
+          <t>10649</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6835</t>
+          <t>7439</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11774</t>
+          <t>11781</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15246</t>
+          <t>15428</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21557</t>
+          <t>21799</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>91,02%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>5722</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14448</t>
+          <t>14888</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12891</t>
+          <t>12731</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11377</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23841</t>
+          <t>23900</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,22%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34195</t>
+          <t>33755</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42848</t>
+          <t>42921</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>46019</t>
+          <t>46179</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>55085</t>
+          <t>54796</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>83711</t>
+          <t>83652</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>96175</t>
+          <t>96192</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,44%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7871</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7721</t>
+          <t>7009</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12094</t>
+          <t>12262</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,87%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20774</t>
+          <t>20928</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27241</t>
+          <t>27205</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19708</t>
+          <t>20420</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26021</t>
+          <t>26073</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43980</t>
+          <t>43812</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52420</t>
+          <t>52398</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,44%</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>633</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>5572</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>26,72%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9670</t>
+          <t>9680</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15745</t>
+          <t>15279</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20232</t>
+          <t>20218</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18215</t>
+          <t>18169</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33639</t>
+          <t>32549</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13066</t>
+          <t>13008</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27429</t>
+          <t>27172</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35131</t>
+          <t>35215</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55455</t>
+          <t>55742</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>105999</t>
+          <t>107089</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>121423</t>
+          <t>121469</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>119250</t>
+          <t>119507</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>133613</t>
+          <t>133671</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>230861</t>
+          <t>230574</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>251185</t>
+          <t>251101</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,7%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>747</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6623</t>
+          <t>6508</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4773</t>
+          <t>4916</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8749</t>
+          <t>8569</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9220</t>
+          <t>9335</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15081</t>
+          <t>15096</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12971</t>
+          <t>12828</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24838</t>
+          <t>25018</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31551</t>
+          <t>31557</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,96%</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>714</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12954</t>
+          <t>12605</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24515</t>
+          <t>24782</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30312</t>
+          <t>30343</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,7%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>707</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>633</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>5654</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13576</t>
+          <t>13459</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18447</t>
+          <t>18480</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2831</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9675</t>
+          <t>9465</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6860</t>
+          <t>7182</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13622</t>
+          <t>14036</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,33%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36814</t>
+          <t>37024</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43658</t>
+          <t>44142</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27664</t>
+          <t>27342</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33285</t>
+          <t>33297</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67391</t>
+          <t>66977</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>76317</t>
+          <t>76158</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,01%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>602</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10435</t>
+          <t>10461</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13313</t>
+          <t>14044</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>26,86%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20103</t>
+          <t>20766</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26012</t>
+          <t>26019</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15227</t>
+          <t>15201</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22817</t>
+          <t>22732</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38969</t>
+          <t>38238</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47860</t>
+          <t>47552</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>90,95%</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>555</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10129</t>
+          <t>10021</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6034</t>
+          <t>5898</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18066</t>
+          <t>18421</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22254</t>
+          <t>22248</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8838</t>
+          <t>8983</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19797</t>
+          <t>19810</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9682</t>
+          <t>9715</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21537</t>
+          <t>22006</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21567</t>
+          <t>20572</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37352</t>
+          <t>36468</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,2%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>103023</t>
+          <t>103010</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>113982</t>
+          <t>113837</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>95498</t>
+          <t>95029</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>107353</t>
+          <t>107320</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>202503</t>
+          <t>203387</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>218288</t>
+          <t>219283</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,42%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6417</t>
+          <t>6394</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6317</t>
+          <t>6797</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9815</t>
+          <t>10125</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18435</t>
+          <t>18458</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23709</t>
+          <t>23783</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25084</t>
+          <t>24604</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46438</t>
+          <t>46128</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54090</t>
+          <t>53990</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>4998</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>392</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20287</t>
+          <t>20176</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18417</t>
+          <t>18494</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40963</t>
+          <t>40972</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46507</t>
+          <t>46532</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -9364,7 +9364,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3493</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13803</t>
+          <t>13264</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22876</t>
+          <t>23047</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2273</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18517</t>
+          <t>19348</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8196</t>
+          <t>7577</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22306</t>
+          <t>22611</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57864</t>
+          <t>57033</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74108</t>
+          <t>74050</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47648</t>
+          <t>48267</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54785</t>
+          <t>54819</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>109919</t>
+          <t>109614</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>126961</t>
+          <t>127518</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -10015,7 +10015,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>4068</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>382</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4730</t>
+          <t>5648</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -10123,7 +10123,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27122</t>
+          <t>26882</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31201</t>
+          <t>31909</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60153</t>
+          <t>59235</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>64521</t>
+          <t>64501</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>583</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4341</t>
+          <t>4229</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>940</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>7130</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11631</t>
+          <t>11638</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10958</t>
+          <t>11070</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20766</t>
+          <t>20390</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>26266</t>
+          <t>26580</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7802</t>
+          <t>7875</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24974</t>
+          <t>26025</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>5287</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16375</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16964</t>
+          <t>15327</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37441</t>
+          <t>37884</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>150413</t>
+          <t>149362</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>167585</t>
+          <t>167512</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>162934</t>
+          <t>162845</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>173716</t>
+          <t>174022</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>317256</t>
+          <t>316813</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>337733</t>
+          <t>339370</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
